--- a/artfynd/A 38419-2021 artfynd.xlsx
+++ b/artfynd/A 38419-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38419-2021 artfynd.xlsx
+++ b/artfynd/A 38419-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6195607</v>
+        <v>479919</v>
       </c>
       <c r="B2" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,30 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224358</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>500 m NNO Dalsätter, Srm</t>
+          <t>Höglunda, 200 m SV om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620653.4293846504</v>
+        <v>620443</v>
       </c>
       <c r="R2" t="n">
-        <v>6539172.36384617</v>
+        <v>6539135</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -741,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2005-08-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-11-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-08-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-11-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,66 +756,87 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>blandbarrskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anneli Kihl</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anneli Kihl, Staffan Kihl</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>479919</v>
+        <v>87806531</v>
       </c>
       <c r="B3" t="n">
-        <v>93374</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>42406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100173</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Treuddsaftonfly</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Acronicta tridens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Höglunda, 200 m SV om, Srm</t>
+          <t>500 m NNO Dalsätter, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620442.7102644799</v>
+        <v>620653</v>
       </c>
       <c r="R3" t="n">
-        <v>6539134.798178834</v>
+        <v>6539172</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -853,22 +863,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2009-11-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2009-11-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,69 +877,101 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>blandbarrskog</t>
+          <t>Vägkant längs skogsväg med alsly, björksly, aspsly och hallon.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Anneli Kihl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Anneli Kihl, Staffan Kihl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6221965</v>
+        <v>86070905</v>
       </c>
       <c r="B4" t="n">
-        <v>95520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>61491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224363</v>
+        <v>106670</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Arion ater ater</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Höglunda, 300 m VSV om, Srm</t>
+          <t>500 m NNO Dalsätter, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620442.7102644799</v>
+        <v>620653</v>
       </c>
       <c r="R4" t="n">
-        <v>6539134.798178834</v>
+        <v>6539172</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -966,22 +998,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2009-11-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2009-11-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,97 +1012,67 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>blandbarrskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Anneli Kihl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Anneli Kihl, Staffan Kihl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>87806531</v>
+        <v>111018867</v>
       </c>
       <c r="B5" t="n">
-        <v>41705</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100173</v>
+        <v>222133</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Treuddsaftonfly</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Acronicta tridens</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>500 m NNO Dalsätter, Srm</t>
+          <t>Rosenberg mot Dalsätter, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620653.4293846504</v>
+        <v>620653</v>
       </c>
       <c r="R5" t="n">
-        <v>6539172.36384617</v>
+        <v>6539094</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,22 +1096,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,42 +1110,217 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Vägkant längs skogsväg med alsly, björksly, aspsly och hallon.</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
+          <t>vägkant i skog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6195607</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97990</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>224358</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig plattlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum subsp. complanatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>500 m NNO Dalsätter, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>620653</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6539172</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ludgo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2005-08-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2005-08-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Anneli Kihl</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Anneli Kihl, Staffan Kihl</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6221965</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Höglunda, 300 m VSV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>620443</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6539135</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ludgo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2009-11-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2009-11-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>blandbarrskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
